--- a/outputs/evaluation/decision/v2/CF_M01/run_2/CF_M01_decision_eval_llm_report.xlsx
+++ b/outputs/evaluation/decision/v2/CF_M01/run_2/CF_M01_decision_eval_llm_report.xlsx
@@ -476,12 +476,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Amazon Athena is a serverless service that makes it unnecessary to manage infrastructure when there is an increase in the data set and users. In addition, to obtain data quickly, Athena performs queries in parallel.</t>
+          <t>This service, being a serverless service, means that it is not necessary to manage the infrastructure when there is an increase in the set of data and users.</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>C_01, Performance</t>
+          <t>C_03, Scalability</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -496,7 +496,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>12a. Speed and latency; Performance</t>
+          <t>12f. Capacity; Scalability</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -506,16 +506,16 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>CF_M01_AD07</t>
+          <t>CF_M01_AD02</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>To ensure the fastest possible data transmission, two Amazon services have been used, which allow us to perform a transmission in almost real time.</t>
+          <t>Increases system security [...] It is only the Api Gateway that is responsible for authorization and SSL with the client</t>
         </is>
       </c>
       <c r="J2" t="n">
-        <v>0.6716</v>
+        <v>0.6661</v>
       </c>
     </row>
   </sheetData>
